--- a/results/DR_results/01_pollution_assessment/HZD_Focus/tables/stressor_cutoff_metrics.xlsx
+++ b/results/DR_results/01_pollution_assessment/HZD_Focus/tables/stressor_cutoff_metrics.xlsx
@@ -491,28 +491,28 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6311557262242945</v>
+        <v>0.614131995287978</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.213065642654233</v>
+        <v>-1.315208028272132</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3422342549951632</v>
+        <v>0.3183119552740906</v>
       </c>
       <c r="G2" t="n">
-        <v>0.97</v>
+        <v>0.971</v>
       </c>
       <c r="H2" t="n">
-        <v>102.2406059199136</v>
+        <v>97.51135459172052</v>
       </c>
       <c r="I2" t="n">
-        <v>161.9895085663538</v>
+        <v>158.7791473818191</v>
       </c>
       <c r="J2" t="n">
-        <v>9.757432796247812</v>
+        <v>10.00543501114308</v>
       </c>
       <c r="K2" t="n">
-        <v>64.04063328615135</v>
+        <v>43.07465261959182</v>
       </c>
     </row>
     <row r="3">
@@ -628,31 +628,31 @@
         <v>0.13</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>146</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3877318959169668</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1326201858823696</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F6" t="n">
-        <v>1.51985142455587</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G6" t="n">
-        <v>0.13</v>
+        <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>166.682327235339</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I6" t="n">
-        <v>429.8906770131551</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J6" t="n">
-        <v>6.969729952545892</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K6" t="n">
-        <v>7.121975103600141</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -663,31 +663,31 @@
         <v>0.15</v>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2101739035363048</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.05310146195159349</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7983044792163264</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G7" t="n">
-        <v>0.673</v>
+        <v>0.001</v>
       </c>
       <c r="H7" t="n">
-        <v>107.0510683521782</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I7" t="n">
-        <v>509.3451972437034</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J7" t="n">
-        <v>2.361983061799055</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K7" t="n">
-        <v>6.166535133627305</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -698,31 +698,31 @@
         <v>0.17</v>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>146</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1935325165363683</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.03048622887019592</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8639121524635467</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G8" t="n">
-        <v>0.622</v>
+        <v>0.001</v>
       </c>
       <c r="H8" t="n">
-        <v>118.0486740680034</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I8" t="n">
-        <v>609.9681654571978</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J8" t="n">
-        <v>2.055728694702113</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K8" t="n">
-        <v>6.148404615207265</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -733,31 +733,31 @@
         <v>0.19</v>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1870412713908489</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.00652033065894897</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9663139249215785</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G9" t="n">
-        <v>0.514</v>
+        <v>0.001</v>
       </c>
       <c r="H9" t="n">
-        <v>123.6542313257587</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I9" t="n">
-        <v>661.1066659580488</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J9" t="n">
-        <v>2.05809172369564</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K9" t="n">
-        <v>2.49525179970926</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -768,31 +768,31 @@
         <v>0.21</v>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>146</v>
       </c>
       <c r="D10" t="n">
-        <v>0.165110632130628</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.008824652842157832</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9492647346193238</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G10" t="n">
-        <v>0.532</v>
+        <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>127.6101228830033</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I10" t="n">
-        <v>772.8764721949825</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J10" t="n">
-        <v>1.966290308324071</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K10" t="n">
-        <v>2.35056451977375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -803,31 +803,31 @@
         <v>0.23</v>
       </c>
       <c r="C11" t="n">
-        <v>33</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1335880946705513</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.02685855446453189</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8326013375204919</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G11" t="n">
-        <v>0.68</v>
+        <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>113.576928593518</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I11" t="n">
-        <v>850.2024740574084</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J11" t="n">
-        <v>1.710658650297028</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K11" t="n">
-        <v>2.47532144204589</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -838,31 +838,31 @@
         <v>0.25</v>
       </c>
       <c r="C12" t="n">
-        <v>36</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1330408863546525</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.01145229925290558</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9207415961884203</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G12" t="n">
-        <v>0.543</v>
+        <v>0.001</v>
       </c>
       <c r="H12" t="n">
-        <v>127.0010827543832</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I12" t="n">
-        <v>954.6018989668426</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J12" t="n">
-        <v>1.867286000686359</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K12" t="n">
-        <v>2.089308255927368</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -873,31 +873,31 @@
         <v>0.27</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>146</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1187590025951851</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.01476236064796876</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8894382120628507</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G13" t="n">
-        <v>0.599</v>
+        <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>118.7003303247927</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I13" t="n">
-        <v>999.5059551772051</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J13" t="n">
-        <v>1.674742141630445</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K13" t="n">
-        <v>2.038730395541476</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -908,31 +908,31 @@
         <v>0.29</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>146</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1226253655091594</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0007677773854315451</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F14" t="n">
-        <v>1.006300612027968</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G14" t="n">
-        <v>0.441</v>
+        <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>128.6358366558066</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I14" t="n">
-        <v>1049.014909123335</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J14" t="n">
-        <v>1.752900022665566</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K14" t="n">
-        <v>2.081641419775443</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -943,31 +943,31 @@
         <v>0.31</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1151382916126999</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001694482845097212</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F15" t="n">
-        <v>1.014936759118944</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G15" t="n">
-        <v>0.437</v>
+        <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>129.4307763823299</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I15" t="n">
-        <v>1124.13320164335</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J15" t="n">
-        <v>1.593986964207741</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K15" t="n">
-        <v>1.86290054114326</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -978,31 +978,31 @@
         <v>0.33</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>146</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1089401425568524</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002861588099334789</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F16" t="n">
-        <v>1.02697612268539</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G16" t="n">
-        <v>0.422</v>
+        <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>132.0804993917316</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I16" t="n">
-        <v>1212.413498750499</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J16" t="n">
-        <v>1.496629075095999</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K16" t="n">
-        <v>1.865343661491237</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1013,31 +1013,31 @@
         <v>0.35</v>
       </c>
       <c r="C17" t="n">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="D17" t="n">
-        <v>0.122282184208932</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02475798245436889</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F17" t="n">
-        <v>1.253865010007226</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G17" t="n">
-        <v>0.177</v>
+        <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>161.1991654313688</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I17" t="n">
-        <v>1318.255528997937</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J17" t="n">
-        <v>1.937483360487856</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K17" t="n">
-        <v>1.822359832423708</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1048,31 +1048,31 @@
         <v>0.37</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1122614833144513</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01978872115970653</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F18" t="n">
-        <v>1.213995134335795</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G18" t="n">
-        <v>0.239</v>
+        <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>159.037591440822</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I18" t="n">
-        <v>1416.671032177154</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J18" t="n">
-        <v>1.824386625004886</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K18" t="n">
-        <v>1.80639832870398</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1083,31 +1083,31 @@
         <v>0.39</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>146</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1167427710068502</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02841704810753509</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F19" t="n">
-        <v>1.321730150342824</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G19" t="n">
-        <v>0.151</v>
+        <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>169.0642844468662</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I19" t="n">
-        <v>1448.177758577838</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J19" t="n">
-        <v>2.013139814134985</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K19" t="n">
-        <v>1.79159752193912</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1118,31 +1118,31 @@
         <v>0.41</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1241986422543876</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04157587265574492</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F20" t="n">
-        <v>1.503201149727955</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G20" t="n">
-        <v>0.09</v>
+        <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>188.504996224059</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I20" t="n">
-        <v>1517.770184942578</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J20" t="n">
-        <v>2.168141727410586</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K20" t="n">
-        <v>1.714909604630723</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1153,31 +1153,31 @@
         <v>0.43</v>
       </c>
       <c r="C21" t="n">
-        <v>62</v>
+        <v>146</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1292170146636983</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05146853383009997</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F21" t="n">
-        <v>1.661987646295697</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G21" t="n">
-        <v>0.031</v>
+        <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>209.4372532623449</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I21" t="n">
-        <v>1620.817922526912</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J21" t="n">
-        <v>2.216412665762693</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K21" t="n">
-        <v>1.672117513588483</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1188,31 +1188,31 @@
         <v>0.45</v>
       </c>
       <c r="C22" t="n">
-        <v>65</v>
+        <v>146</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1400721778071097</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06719693863822063</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F22" t="n">
-        <v>1.922081895093217</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G22" t="n">
-        <v>0.011</v>
+        <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>244.2363362843794</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I22" t="n">
-        <v>1743.646312265609</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J22" t="n">
-        <v>2.122584787349348</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K22" t="n">
-        <v>1.625692931005671</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1223,31 +1223,31 @@
         <v>0.47</v>
       </c>
       <c r="C23" t="n">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1367245397215937</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E23" t="n">
-        <v>0.06710555098946425</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F23" t="n">
-        <v>1.963897238548864</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>248.3085678905488</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I23" t="n">
-        <v>1816.122902268817</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J23" t="n">
-        <v>2.148362773887741</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K23" t="n">
-        <v>1.612983655803395</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1258,31 +1258,31 @@
         <v>0.49</v>
       </c>
       <c r="C24" t="n">
-        <v>71</v>
+        <v>146</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1283195983211907</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06126725973051306</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F24" t="n">
-        <v>1.913722936712473</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G24" t="n">
-        <v>0.011</v>
+        <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>242.8597076962711</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I24" t="n">
-        <v>1892.615865959777</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J24" t="n">
-        <v>1.967641527931827</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K24" t="n">
-        <v>1.589628379212215</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1293,31 +1293,31 @@
         <v>0.51</v>
       </c>
       <c r="C25" t="n">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1432515838752182</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08025537680721961</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F25" t="n">
-        <v>2.273971569758021</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>294.819019690253</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I25" t="n">
-        <v>2058.050680591848</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J25" t="n">
-        <v>1.938197204943422</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K25" t="n">
-        <v>1.557237215039431</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1328,31 +1328,31 @@
         <v>0.53</v>
       </c>
       <c r="C26" t="n">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1312979508017879</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07012175015402655</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F26" t="n">
-        <v>2.146225973688224</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G26" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>278.22117477166</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I26" t="n">
-        <v>2119.006222661256</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J26" t="n">
-        <v>1.776211150265146</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K26" t="n">
-        <v>1.531487097628413</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1363,31 +1363,31 @@
         <v>0.55</v>
       </c>
       <c r="C27" t="n">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1198956453913468</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06042913494481617</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F27" t="n">
-        <v>2.016187674222975</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G27" t="n">
-        <v>0.014</v>
+        <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>262.7074798175631</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I27" t="n">
-        <v>2191.134456635766</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J27" t="n">
-        <v>1.710912663196865</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K27" t="n">
-        <v>1.530264343880808</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1398,31 +1398,31 @@
         <v>0.57</v>
       </c>
       <c r="C28" t="n">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1224314004232946</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06544642642480736</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F28" t="n">
-        <v>2.148485676707416</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G28" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>278.4552980276093</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I28" t="n">
-        <v>2274.378117581578</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J28" t="n">
-        <v>1.836851764641551</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K28" t="n">
-        <v>1.501165171652945</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1433,31 +1433,31 @@
         <v>0.59</v>
       </c>
       <c r="C29" t="n">
-        <v>86</v>
+        <v>146</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1132483323098678</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E29" t="n">
-        <v>0.05782635307923445</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F29" t="n">
-        <v>2.043383038317626</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G29" t="n">
-        <v>0.013</v>
+        <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>265.9138555290026</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I29" t="n">
-        <v>2348.059791303721</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J29" t="n">
-        <v>1.786473642217435</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K29" t="n">
-        <v>1.494350283823733</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1468,31 +1468,31 @@
         <v>0.61</v>
       </c>
       <c r="C30" t="n">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="D30" t="n">
-        <v>0.105873062647903</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E30" t="n">
-        <v>0.05200999413271634</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F30" t="n">
-        <v>1.965596568603445</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G30" t="n">
-        <v>0.018</v>
+        <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>252.7171660325977</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I30" t="n">
-        <v>2386.982672571277</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J30" t="n">
-        <v>1.682460683080051</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K30" t="n">
-        <v>1.483904730331222</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1503,31 +1503,31 @@
         <v>0.63</v>
       </c>
       <c r="C31" t="n">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="D31" t="n">
-        <v>0.09980584361051441</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E31" t="n">
-        <v>0.04685324617583875</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F31" t="n">
-        <v>1.884814880585202</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G31" t="n">
-        <v>0.019</v>
+        <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>242.5199579559856</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I31" t="n">
-        <v>2429.917419489017</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J31" t="n">
-        <v>1.656029153670766</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K31" t="n">
-        <v>1.464472200768956</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1538,31 +1538,31 @@
         <v>0.65</v>
       </c>
       <c r="C32" t="n">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1120660564937226</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06161526424904773</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F32" t="n">
-        <v>2.221294285136847</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G32" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>286.444156414047</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I32" t="n">
-        <v>2556.029589834743</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J32" t="n">
-        <v>1.971791286466446</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K32" t="n">
-        <v>1.389287120715062</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1573,31 +1573,31 @@
         <v>0.67</v>
       </c>
       <c r="C33" t="n">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1065828112413874</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E33" t="n">
-        <v>0.05749395471618879</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F33" t="n">
-        <v>2.171222122207631</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G33" t="n">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>282.3398311779272</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I33" t="n">
-        <v>2649.018428857985</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J33" t="n">
-        <v>1.942425308726367</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K33" t="n">
-        <v>1.35372601686378</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1608,31 +1608,31 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="D34" t="n">
-        <v>0.09974849947785841</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E34" t="n">
-        <v>0.05186278136497857</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F34" t="n">
-        <v>2.083053223567069</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G34" t="n">
-        <v>0.012</v>
+        <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>270.1923442618073</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I34" t="n">
-        <v>2708.735927619473</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J34" t="n">
-        <v>1.79163312462967</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K34" t="n">
-        <v>1.319040408972599</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1643,31 +1643,31 @@
         <v>0.71</v>
       </c>
       <c r="C35" t="n">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="D35" t="n">
-        <v>0.09732881163805379</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E35" t="n">
-        <v>0.05079936893898429</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F35" t="n">
-        <v>2.091768265257997</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G35" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>270.8712643885596</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I35" t="n">
-        <v>2783.053238088174</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J35" t="n">
-        <v>1.7732549196618</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K35" t="n">
-        <v>1.262101061080883</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1678,31 +1678,31 @@
         <v>0.73</v>
       </c>
       <c r="C36" t="n">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1064871195908077</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E36" t="n">
-        <v>0.06181147557034805</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F36" t="n">
-        <v>2.383560929575879</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G36" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>310.0765594703663</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I36" t="n">
-        <v>2911.869159968648</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J36" t="n">
-        <v>1.943888611544185</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K36" t="n">
-        <v>1.201408981136851</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1713,31 +1713,31 @@
         <v>0.75</v>
       </c>
       <c r="C37" t="n">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1029493963171701</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E37" t="n">
-        <v>0.05940325050732398</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F37" t="n">
-        <v>2.364144849161196</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G37" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>307.7791891702543</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I37" t="n">
-        <v>2989.616259837381</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J37" t="n">
-        <v>1.972613786196539</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K37" t="n">
-        <v>1.169621546076444</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1748,31 +1748,31 @@
         <v>0.77</v>
       </c>
       <c r="C38" t="n">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1010051593489569</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E38" t="n">
-        <v>0.05859974233711518</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F38" t="n">
-        <v>2.381892844509732</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G38" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>312.5279545254729</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I38" t="n">
-        <v>3094.178124562311</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J38" t="n">
-        <v>1.942611094132762</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K38" t="n">
-        <v>1.112333708524218</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1783,31 +1783,31 @@
         <v>0.79</v>
       </c>
       <c r="C39" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="D39" t="n">
-        <v>0.09962338595944409</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E39" t="n">
-        <v>0.05832170641629941</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F39" t="n">
-        <v>2.412090429769933</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>316.2808157810634</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I39" t="n">
-        <v>3174.764767680341</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J39" t="n">
-        <v>1.922306557140786</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K39" t="n">
-        <v>1.10896372231046</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1818,31 +1818,31 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1034032255999831</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E40" t="n">
-        <v>0.06337658388569667</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F40" t="n">
-        <v>2.583360011516431</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>338.2084897491986</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I40" t="n">
-        <v>3270.773109705136</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J40" t="n">
-        <v>2.074953645089999</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K40" t="n">
-        <v>1.097775345676716</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1853,31 +1853,31 @@
         <v>0.83</v>
       </c>
       <c r="C41" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="D41" t="n">
-        <v>0.111187453546446</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E41" t="n">
-        <v>0.07254342978759587</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F41" t="n">
-        <v>2.877222471456071</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>374.3426893263465</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I41" t="n">
-        <v>3366.770956490818</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J41" t="n">
-        <v>2.249261814172323</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K41" t="n">
-        <v>1.086116815599792</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1888,31 +1888,31 @@
         <v>0.85</v>
       </c>
       <c r="C42" t="n">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1156634967857022</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E42" t="n">
-        <v>0.07819161105628269</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F42" t="n">
-        <v>3.086674036660344</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G42" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>399.2932296118111</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I42" t="n">
-        <v>3452.197458214579</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J42" t="n">
-        <v>2.384032491207493</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K42" t="n">
-        <v>1.067035660908041</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1923,31 +1923,31 @@
         <v>0.87</v>
       </c>
       <c r="C43" t="n">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1162044887409279</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E43" t="n">
-        <v>0.07968401306906536</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F43" t="n">
-        <v>3.1818996495289</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G43" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>408.5945809048446</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I43" t="n">
-        <v>3516.168655203894</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J43" t="n">
-        <v>2.317508018674296</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K43" t="n">
-        <v>1.057487479517155</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1958,31 +1958,31 @@
         <v>0.89</v>
       </c>
       <c r="C44" t="n">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1176302959077755</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E44" t="n">
-        <v>0.08176160874955496</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F44" t="n">
-        <v>3.279470346625623</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>424.3490391051785</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I44" t="n">
-        <v>3607.48084352246</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J44" t="n">
-        <v>2.409537556219933</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K44" t="n">
-        <v>1.042213827164324</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1993,31 +1993,31 @@
         <v>0.91</v>
       </c>
       <c r="C45" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1148827311573338</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E45" t="n">
-        <v>0.07975903001278351</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F45" t="n">
-        <v>3.270803685651986</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>426.1797208964989</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I45" t="n">
-        <v>3709.69349878041</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J45" t="n">
-        <v>2.461431042713706</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K45" t="n">
-        <v>1.029645445180832</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2028,31 +2028,31 @@
         <v>0.93</v>
       </c>
       <c r="C46" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1166181951220964</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E46" t="n">
-        <v>0.08237859028186745</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F46" t="n">
-        <v>3.405944538970826</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>443.5951767640169</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I46" t="n">
-        <v>3803.824748784559</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J46" t="n">
-        <v>2.571689052700447</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K46" t="n">
-        <v>1.019881646091181</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2063,31 +2063,31 @@
         <v>0.95</v>
       </c>
       <c r="C47" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1172526640041853</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E47" t="n">
-        <v>0.08381526491343483</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F47" t="n">
-        <v>3.50663230970676</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>457.1488266603753</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I47" t="n">
-        <v>3898.835310420389</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J47" t="n">
-        <v>2.505645453857833</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K47" t="n">
-        <v>1.015612943584335</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2098,31 +2098,31 @@
         <v>0.97</v>
       </c>
       <c r="C48" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D48" t="n">
-        <v>0.113066011511225</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E48" t="n">
-        <v>0.08021660453015944</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F48" t="n">
-        <v>3.441949852440131</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>450.442211921338</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I48" t="n">
-        <v>3983.886986909578</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J48" t="n">
-        <v>2.413107483344004</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K48" t="n">
-        <v>1.009005070522143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2133,31 +2133,31 @@
         <v>0.99</v>
       </c>
       <c r="C49" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1124587507331253</v>
+        <v>0.1174386265196101</v>
       </c>
       <c r="E49" t="n">
-        <v>0.08030145909302122</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="F49" t="n">
-        <v>3.497146214666759</v>
+        <v>3.725838951666003</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>456.5849261555256</v>
+        <v>486.2494275501598</v>
       </c>
       <c r="I49" t="n">
-        <v>4060.02132496601</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J49" t="n">
-        <v>2.395549611936618</v>
+        <v>2.554849059789079</v>
       </c>
       <c r="K49" t="n">
-        <v>1.001440125335337</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
